--- a/backend/assets/nakladnoy/warehouse/700-wh-7.0.0.xlsx
+++ b/backend/assets/nakladnoy/warehouse/700-wh-7.0.0.xlsx
@@ -5006,6 +5006,6 @@
     <mergeCell ref="A287:B287"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>